--- a/Team-Data/2012-13/4-5-2012-13.xlsx
+++ b/Team-Data/2012-13/4-5-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E2" t="n">
         <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>0.545</v>
+        <v>0.553</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
@@ -679,7 +746,7 @@
         <v>37.5</v>
       </c>
       <c r="J2" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K2" t="n">
         <v>0.465</v>
@@ -691,22 +758,22 @@
         <v>23.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="O2" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="P2" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.707</v>
+        <v>0.709</v>
       </c>
       <c r="R2" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T2" t="n">
         <v>40.6</v>
@@ -718,7 +785,7 @@
         <v>15</v>
       </c>
       <c r="W2" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X2" t="n">
         <v>4.6</v>
@@ -733,16 +800,16 @@
         <v>18.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF2" t="n">
         <v>13</v>
@@ -787,22 +854,22 @@
         <v>10</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW2" t="n">
         <v>15</v>
       </c>
       <c r="AX2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ2" t="n">
         <v>2</v>
@@ -814,7 +881,7 @@
         <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E3" t="n">
         <v>39</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>0.513</v>
+        <v>0.52</v>
       </c>
       <c r="H3" t="n">
         <v>49.1</v>
@@ -861,31 +928,31 @@
         <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L3" t="n">
         <v>6.1</v>
       </c>
       <c r="M3" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O3" t="n">
         <v>16.5</v>
       </c>
       <c r="P3" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.775</v>
+        <v>0.778</v>
       </c>
       <c r="R3" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="S3" t="n">
         <v>31.4</v>
@@ -897,16 +964,16 @@
         <v>22.8</v>
       </c>
       <c r="V3" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z3" t="n">
         <v>21.3</v>
@@ -915,22 +982,22 @@
         <v>19.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -942,46 +1009,46 @@
         <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM3" t="n">
         <v>26</v>
       </c>
       <c r="AN3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO3" t="n">
         <v>18</v>
       </c>
-      <c r="AO3" t="n">
-        <v>17</v>
-      </c>
       <c r="AP3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -996,7 +1063,7 @@
         <v>19</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AE4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF4" t="n">
         <v>9</v>
       </c>
       <c r="AG4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH4" t="n">
         <v>8</v>
@@ -1130,7 +1197,7 @@
         <v>9</v>
       </c>
       <c r="AM4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN4" t="n">
         <v>15</v>
@@ -1160,13 +1227,13 @@
         <v>19</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
         <v>4</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E5" t="n">
         <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5" t="n">
-        <v>0.237</v>
+        <v>0.24</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J5" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.421</v>
+        <v>0.423</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
@@ -1237,28 +1304,28 @@
         <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>0.334</v>
+        <v>0.336</v>
       </c>
       <c r="O5" t="n">
         <v>19.1</v>
       </c>
       <c r="P5" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.749</v>
+        <v>0.747</v>
       </c>
       <c r="R5" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S5" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="T5" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U5" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="V5" t="n">
         <v>13.9</v>
@@ -1273,19 +1340,19 @@
         <v>7.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.3</v>
+        <v>93.5</v>
       </c>
       <c r="AC5" t="n">
         <v>-9.699999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1303,7 +1370,7 @@
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1318,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="AO5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP5" t="n">
         <v>4</v>
@@ -1336,13 +1403,13 @@
         <v>27</v>
       </c>
       <c r="AU5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV5" t="n">
         <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
         <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
@@ -1413,31 +1480,31 @@
         <v>0.436</v>
       </c>
       <c r="L6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="O6" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P6" t="n">
         <v>21.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.776</v>
+        <v>0.774</v>
       </c>
       <c r="R6" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S6" t="n">
         <v>30.6</v>
       </c>
       <c r="T6" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U6" t="n">
         <v>23</v>
@@ -1455,22 +1522,22 @@
         <v>5.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="n">
         <v>11</v>
@@ -1485,7 +1552,7 @@
         <v>26</v>
       </c>
       <c r="AJ6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK6" t="n">
         <v>27</v>
@@ -1500,13 +1567,13 @@
         <v>24</v>
       </c>
       <c r="AO6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
         <v>5</v>
@@ -1521,10 +1588,10 @@
         <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX6" t="n">
         <v>12</v>
@@ -1539,10 +1606,10 @@
         <v>18</v>
       </c>
       <c r="BB6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
         <v>52</v>
       </c>
       <c r="G7" t="n">
-        <v>0.307</v>
+        <v>0.297</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
@@ -1589,46 +1656,46 @@
         <v>36.5</v>
       </c>
       <c r="J7" t="n">
-        <v>84.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>0.434</v>
       </c>
       <c r="L7" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M7" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O7" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P7" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.757</v>
+        <v>0.755</v>
       </c>
       <c r="R7" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S7" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T7" t="n">
-        <v>40.7</v>
+        <v>40.5</v>
       </c>
       <c r="U7" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V7" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W7" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X7" t="n">
         <v>3.9</v>
@@ -1640,25 +1707,25 @@
         <v>21.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB7" t="n">
         <v>96.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.6</v>
+        <v>-4.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF7" t="n">
         <v>27</v>
       </c>
       <c r="AG7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH7" t="n">
         <v>26</v>
@@ -1667,7 +1734,7 @@
         <v>19</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK7" t="n">
         <v>28</v>
@@ -1676,7 +1743,7 @@
         <v>17</v>
       </c>
       <c r="AM7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AN7" t="n">
         <v>22</v>
@@ -1688,22 +1755,22 @@
         <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
         <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
         <v>14</v>
@@ -1718,7 +1785,7 @@
         <v>26</v>
       </c>
       <c r="BA7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB7" t="n">
         <v>17</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8" t="n">
         <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>0.487</v>
+        <v>0.48</v>
       </c>
       <c r="H8" t="n">
         <v>48.7</v>
       </c>
       <c r="I8" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J8" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K8" t="n">
         <v>0.461</v>
@@ -1783,7 +1850,7 @@
         <v>20</v>
       </c>
       <c r="N8" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O8" t="n">
         <v>16.4</v>
@@ -1792,7 +1859,7 @@
         <v>20.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.794</v>
+        <v>0.792</v>
       </c>
       <c r="R8" t="n">
         <v>9.199999999999999</v>
@@ -1801,13 +1868,13 @@
         <v>32.5</v>
       </c>
       <c r="T8" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U8" t="n">
         <v>23.1</v>
       </c>
       <c r="V8" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W8" t="n">
         <v>7.9</v>
@@ -1816,31 +1883,31 @@
         <v>5.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z8" t="n">
         <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>101.3</v>
+        <v>101</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
         <v>17</v>
       </c>
       <c r="AF8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
@@ -1849,7 +1916,7 @@
         <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK8" t="n">
         <v>9</v>
@@ -1864,13 +1931,13 @@
         <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP8" t="n">
         <v>24</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR8" t="n">
         <v>26</v>
@@ -1885,7 +1952,7 @@
         <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW8" t="n">
         <v>17</v>
@@ -1894,7 +1961,7 @@
         <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AZ8" t="n">
         <v>23</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>4.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2061,13 +2128,13 @@
         <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>26</v>
@@ -2207,7 +2274,7 @@
         <v>26</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
         <v>24</v>
@@ -2225,7 +2292,7 @@
         <v>23</v>
       </c>
       <c r="AN10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO10" t="n">
         <v>23</v>
@@ -2252,7 +2319,7 @@
         <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX10" t="n">
         <v>16</v>
@@ -2267,10 +2334,10 @@
         <v>16</v>
       </c>
       <c r="BB10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -2299,40 +2366,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
         <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>0.579</v>
+        <v>0.573</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J11" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.401</v>
+        <v>0.399</v>
       </c>
       <c r="O11" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P11" t="n">
         <v>21.5</v>
@@ -2344,10 +2411,10 @@
         <v>10.8</v>
       </c>
       <c r="S11" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="T11" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
       <c r="U11" t="n">
         <v>22.5</v>
@@ -2356,10 +2423,10 @@
         <v>15.1</v>
       </c>
       <c r="W11" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y11" t="n">
         <v>4.9</v>
@@ -2368,16 +2435,16 @@
         <v>21.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>101</v>
+        <v>100.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2416,31 +2483,31 @@
         <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
         <v>14</v>
       </c>
       <c r="AV11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX11" t="n">
         <v>26</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ11" t="n">
         <v>28</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F12" t="n">
         <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
@@ -2499,10 +2566,10 @@
         <v>38.2</v>
       </c>
       <c r="J12" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L12" t="n">
         <v>10.6</v>
@@ -2511,13 +2578,13 @@
         <v>28.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O12" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P12" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q12" t="n">
         <v>0.755</v>
@@ -2526,7 +2593,7 @@
         <v>11.1</v>
       </c>
       <c r="S12" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T12" t="n">
         <v>43.3</v>
@@ -2544,7 +2611,7 @@
         <v>4.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z12" t="n">
         <v>20.2</v>
@@ -2553,16 +2620,16 @@
         <v>20.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.1</v>
+        <v>106</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF12" t="n">
         <v>11</v>
@@ -2580,7 +2647,7 @@
         <v>10</v>
       </c>
       <c r="AK12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL12" t="n">
         <v>2</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2598,7 +2665,7 @@
         <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
@@ -2622,10 +2689,10 @@
         <v>28</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
         <v>11</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -2663,43 +2730,43 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E13" t="n">
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
-        <v>0.632</v>
+        <v>0.64</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J13" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="K13" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L13" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M13" t="n">
         <v>19.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.353</v>
+        <v>0.357</v>
       </c>
       <c r="O13" t="n">
         <v>17.5</v>
       </c>
       <c r="P13" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q13" t="n">
         <v>0.75</v>
@@ -2708,16 +2775,16 @@
         <v>12.9</v>
       </c>
       <c r="S13" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="T13" t="n">
-        <v>46.1</v>
+        <v>46.3</v>
       </c>
       <c r="U13" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V13" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W13" t="n">
         <v>7.1</v>
@@ -2729,22 +2796,22 @@
         <v>5.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA13" t="n">
         <v>21.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF13" t="n">
         <v>8</v>
@@ -2771,13 +2838,13 @@
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="n">
         <v>9</v>
       </c>
       <c r="AP13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
         <v>18</v>
@@ -2786,7 +2853,7 @@
         <v>4</v>
       </c>
       <c r="AS13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
@@ -2795,10 +2862,10 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX13" t="n">
         <v>4</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2935,7 +3002,7 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
@@ -2953,10 +3020,10 @@
         <v>9</v>
       </c>
       <c r="AN14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO14" t="n">
         <v>17</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>16</v>
       </c>
       <c r="AP14" t="n">
         <v>10</v>
@@ -2977,7 +3044,7 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2986,7 +3053,7 @@
         <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ14" t="n">
         <v>25</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F15" t="n">
         <v>36</v>
       </c>
       <c r="G15" t="n">
-        <v>0.526</v>
+        <v>0.52</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3045,25 +3112,25 @@
         <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K15" t="n">
         <v>0.458</v>
       </c>
       <c r="L15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P15" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="Q15" t="n">
         <v>0.6879999999999999</v>
@@ -3099,13 +3166,13 @@
         <v>22.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.1</v>
+        <v>102.3</v>
       </c>
       <c r="AC15" t="n">
         <v>1.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
         <v>14</v>
@@ -3120,10 +3187,10 @@
         <v>28</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK15" t="n">
         <v>10</v>
@@ -3138,7 +3205,7 @@
         <v>16</v>
       </c>
       <c r="AO15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
@@ -3150,25 +3217,25 @@
         <v>13</v>
       </c>
       <c r="AS15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT15" t="n">
         <v>3</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2</v>
       </c>
       <c r="AU15" t="n">
         <v>17</v>
       </c>
       <c r="AV15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ15" t="n">
         <v>3</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" t="n">
         <v>51</v>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G16" t="n">
-        <v>0.671</v>
+        <v>0.68</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3227,7 +3294,7 @@
         <v>36.3</v>
       </c>
       <c r="J16" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0.445</v>
@@ -3239,31 +3306,31 @@
         <v>13.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O16" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="P16" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0.778</v>
       </c>
       <c r="R16" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S16" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T16" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U16" t="n">
         <v>21</v>
       </c>
       <c r="V16" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W16" t="n">
         <v>8.6</v>
@@ -3275,25 +3342,25 @@
         <v>5.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.7</v>
+        <v>93.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
       </c>
       <c r="AF16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG16" t="n">
         <v>5</v>
@@ -3305,7 +3372,7 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK16" t="n">
         <v>19</v>
@@ -3320,10 +3387,10 @@
         <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ16" t="n">
         <v>6</v>
@@ -3335,7 +3402,7 @@
         <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AU16" t="n">
         <v>24</v>
@@ -3347,22 +3414,22 @@
         <v>4</v>
       </c>
       <c r="AX16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB16" t="n">
         <v>26</v>
       </c>
       <c r="BC16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -3391,34 +3458,34 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.787</v>
+        <v>0.784</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J17" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.496</v>
+        <v>0.497</v>
       </c>
       <c r="L17" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M17" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="N17" t="n">
         <v>0.394</v>
@@ -3427,31 +3494,31 @@
         <v>17.5</v>
       </c>
       <c r="P17" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.759</v>
+        <v>0.758</v>
       </c>
       <c r="R17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="S17" t="n">
         <v>30</v>
       </c>
       <c r="T17" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="U17" t="n">
         <v>22.9</v>
       </c>
       <c r="V17" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W17" t="n">
         <v>8.9</v>
       </c>
       <c r="X17" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y17" t="n">
         <v>3.3</v>
@@ -3460,16 +3527,16 @@
         <v>18.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>102.9</v>
+        <v>103.1</v>
       </c>
       <c r="AC17" t="n">
         <v>7.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3496,7 +3563,7 @@
         <v>5</v>
       </c>
       <c r="AM17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN17" t="n">
         <v>2</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV17" t="n">
         <v>3</v>
@@ -3538,7 +3605,7 @@
         <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -3573,49 +3640,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E18" t="n">
         <v>36</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G18" t="n">
-        <v>0.48</v>
+        <v>0.486</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J18" t="n">
-        <v>87.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L18" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
       <c r="O18" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P18" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q18" t="n">
         <v>0.741</v>
       </c>
       <c r="R18" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="S18" t="n">
         <v>30.8</v>
@@ -3624,43 +3691,43 @@
         <v>43.9</v>
       </c>
       <c r="U18" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V18" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W18" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="Y18" t="n">
         <v>4.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA18" t="n">
         <v>19.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.5</v>
+        <v>-1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF18" t="n">
         <v>17</v>
       </c>
       <c r="AG18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH18" t="n">
         <v>15</v>
@@ -3675,13 +3742,13 @@
         <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AN18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO18" t="n">
         <v>25</v>
@@ -3702,13 +3769,13 @@
         <v>5</v>
       </c>
       <c r="AU18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AV18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -3755,25 +3822,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E19" t="n">
         <v>28</v>
       </c>
       <c r="F19" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
-        <v>0.373</v>
+        <v>0.378</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J19" t="n">
-        <v>81.5</v>
+        <v>81.7</v>
       </c>
       <c r="K19" t="n">
         <v>0.44</v>
@@ -3782,28 +3849,28 @@
         <v>5.4</v>
       </c>
       <c r="M19" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.302</v>
+        <v>0.303</v>
       </c>
       <c r="O19" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P19" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="Q19" t="n">
         <v>0.735</v>
       </c>
       <c r="R19" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S19" t="n">
         <v>30.2</v>
       </c>
       <c r="T19" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U19" t="n">
         <v>22.3</v>
@@ -3821,7 +3888,7 @@
         <v>6</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA19" t="n">
         <v>22.7</v>
@@ -3833,16 +3900,16 @@
         <v>-2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF19" t="n">
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
@@ -3851,7 +3918,7 @@
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3875,13 +3942,13 @@
         <v>23</v>
       </c>
       <c r="AR19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS19" t="n">
         <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU19" t="n">
         <v>16</v>
@@ -3890,10 +3957,10 @@
         <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX19" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY19" t="n">
         <v>24</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E20" t="n">
         <v>26</v>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G20" t="n">
-        <v>0.342</v>
+        <v>0.347</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3958,25 +4025,25 @@
         <v>80.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L20" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M20" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O20" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="P20" t="n">
         <v>19.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R20" t="n">
         <v>11.7</v>
@@ -3988,7 +4055,7 @@
         <v>41.3</v>
       </c>
       <c r="U20" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V20" t="n">
         <v>14.4</v>
@@ -4003,19 +4070,19 @@
         <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>94</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
         <v>25</v>
@@ -4030,7 +4097,7 @@
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ20" t="n">
         <v>26</v>
@@ -4045,7 +4112,7 @@
         <v>21</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO20" t="n">
         <v>26</v>
@@ -4060,7 +4127,7 @@
         <v>12</v>
       </c>
       <c r="AS20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT20" t="n">
         <v>19</v>
@@ -4069,7 +4136,7 @@
         <v>22</v>
       </c>
       <c r="AV20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
         <v>30</v>
@@ -4078,7 +4145,7 @@
         <v>8</v>
       </c>
       <c r="AY20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ20" t="n">
         <v>19</v>
@@ -4087,7 +4154,7 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC20" t="n">
         <v>24</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E21" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F21" t="n">
         <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>0.653</v>
+        <v>0.649</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J21" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="K21" t="n">
         <v>0.446</v>
@@ -4146,16 +4213,16 @@
         <v>10.7</v>
       </c>
       <c r="M21" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O21" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P21" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="Q21" t="n">
         <v>0.759</v>
@@ -4164,13 +4231,13 @@
         <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T21" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="U21" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="V21" t="n">
         <v>12.2</v>
@@ -4185,7 +4252,7 @@
         <v>3.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA21" t="n">
         <v>19.4</v>
@@ -4194,10 +4261,10 @@
         <v>99.40000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
         <v>7</v>
@@ -4212,7 +4279,7 @@
         <v>30</v>
       </c>
       <c r="AI21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ21" t="n">
         <v>22</v>
@@ -4230,7 +4297,7 @@
         <v>6</v>
       </c>
       <c r="AO21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP21" t="n">
         <v>16</v>
@@ -4242,13 +4309,13 @@
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -4272,7 +4339,7 @@
         <v>11</v>
       </c>
       <c r="BC21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E22" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F22" t="n">
         <v>20</v>
       </c>
       <c r="G22" t="n">
-        <v>0.737</v>
+        <v>0.733</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4328,40 +4395,40 @@
         <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O22" t="n">
         <v>22.6</v>
       </c>
       <c r="P22" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="Q22" t="n">
         <v>0.827</v>
       </c>
       <c r="R22" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S22" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="T22" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U22" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V22" t="n">
         <v>15.5</v>
       </c>
       <c r="W22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Y22" t="n">
         <v>4</v>
@@ -4373,22 +4440,22 @@
         <v>21.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.8</v>
+        <v>106</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF22" t="n">
         <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH22" t="n">
         <v>12</v>
@@ -4424,7 +4491,7 @@
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
         <v>6</v>
@@ -4433,10 +4500,10 @@
         <v>21</v>
       </c>
       <c r="AV22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E23" t="n">
         <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G23" t="n">
-        <v>0.247</v>
+        <v>0.25</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4501,19 +4568,19 @@
         <v>37.7</v>
       </c>
       <c r="J23" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L23" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M23" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.332</v>
+        <v>0.331</v>
       </c>
       <c r="O23" t="n">
         <v>12.5</v>
@@ -4522,7 +4589,7 @@
         <v>16.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R23" t="n">
         <v>10.6</v>
@@ -4543,22 +4610,22 @@
         <v>6.4</v>
       </c>
       <c r="X23" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y23" t="n">
         <v>5.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA23" t="n">
         <v>16.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.2</v>
+        <v>94.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.7</v>
+        <v>-6.8</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4609,13 +4676,13 @@
         <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW23" t="n">
         <v>29</v>
@@ -4636,7 +4703,7 @@
         <v>23</v>
       </c>
       <c r="BC23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E24" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F24" t="n">
         <v>44</v>
       </c>
       <c r="G24" t="n">
-        <v>0.413</v>
+        <v>0.405</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4683,37 +4750,37 @@
         <v>37.3</v>
       </c>
       <c r="J24" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="K24" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L24" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M24" t="n">
         <v>17.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="O24" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.722</v>
+        <v>0.721</v>
       </c>
       <c r="R24" t="n">
         <v>10.9</v>
       </c>
       <c r="S24" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T24" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U24" t="n">
         <v>22.9</v>
@@ -4737,13 +4804,13 @@
         <v>16.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>93</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.2</v>
+        <v>-3.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4761,7 +4828,7 @@
         <v>13</v>
       </c>
       <c r="AJ24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK24" t="n">
         <v>20</v>
@@ -4773,7 +4840,7 @@
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4794,7 +4861,7 @@
         <v>18</v>
       </c>
       <c r="AU24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4806,16 +4873,16 @@
         <v>19</v>
       </c>
       <c r="AY24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC24" t="n">
         <v>23</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -4847,28 +4914,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G25" t="n">
-        <v>0.303</v>
+        <v>0.307</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J25" t="n">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="K25" t="n">
-        <v>0.443</v>
+        <v>0.441</v>
       </c>
       <c r="L25" t="n">
         <v>5.7</v>
@@ -4877,7 +4944,7 @@
         <v>17.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.325</v>
+        <v>0.324</v>
       </c>
       <c r="O25" t="n">
         <v>14.7</v>
@@ -4886,16 +4953,16 @@
         <v>19.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="R25" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S25" t="n">
         <v>29.9</v>
       </c>
       <c r="T25" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U25" t="n">
         <v>22.4</v>
@@ -4913,37 +4980,37 @@
         <v>5</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA25" t="n">
         <v>18.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC25" t="n">
         <v>-6.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
       </c>
       <c r="AF25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH25" t="n">
         <v>17</v>
       </c>
       <c r="AI25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK25" t="n">
         <v>23</v>
@@ -4979,7 +5046,7 @@
         <v>15</v>
       </c>
       <c r="AV25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW25" t="n">
         <v>16</v>
@@ -5000,7 +5067,7 @@
         <v>22</v>
       </c>
       <c r="BC25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E26" t="n">
         <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G26" t="n">
-        <v>0.434</v>
+        <v>0.44</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
@@ -5047,37 +5114,37 @@
         <v>36.8</v>
       </c>
       <c r="J26" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K26" t="n">
         <v>0.449</v>
       </c>
       <c r="L26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>23.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.353</v>
+        <v>0.356</v>
       </c>
       <c r="O26" t="n">
         <v>16</v>
       </c>
       <c r="P26" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R26" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S26" t="n">
         <v>30.3</v>
       </c>
       <c r="T26" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U26" t="n">
         <v>21.8</v>
@@ -5104,10 +5171,10 @@
         <v>97.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.6</v>
+        <v>-2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5119,25 +5186,25 @@
         <v>19</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK26" t="n">
         <v>14</v>
       </c>
       <c r="AL26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM26" t="n">
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO26" t="n">
         <v>22</v>
@@ -5146,7 +5213,7 @@
         <v>25</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR26" t="n">
         <v>21</v>
@@ -5155,25 +5222,25 @@
         <v>16</v>
       </c>
       <c r="AT26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU26" t="n">
         <v>19</v>
       </c>
       <c r="AV26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW26" t="n">
         <v>28</v>
       </c>
       <c r="AX26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY26" t="n">
         <v>7</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA26" t="n">
         <v>25</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -5211,43 +5278,43 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E27" t="n">
         <v>27</v>
       </c>
       <c r="F27" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G27" t="n">
-        <v>0.355</v>
+        <v>0.36</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J27" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K27" t="n">
         <v>0.448</v>
       </c>
       <c r="L27" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M27" t="n">
         <v>20.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="O27" t="n">
         <v>17.6</v>
       </c>
       <c r="P27" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q27" t="n">
         <v>0.771</v>
@@ -5259,7 +5326,7 @@
         <v>29</v>
       </c>
       <c r="T27" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="U27" t="n">
         <v>20.7</v>
@@ -5271,10 +5338,10 @@
         <v>8.1</v>
       </c>
       <c r="X27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z27" t="n">
         <v>21</v>
@@ -5283,13 +5350,13 @@
         <v>20.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.1</v>
+        <v>100</v>
       </c>
       <c r="AC27" t="n">
         <v>-4.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5319,7 +5386,7 @@
         <v>11</v>
       </c>
       <c r="AN27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO27" t="n">
         <v>8</v>
@@ -5337,13 +5404,13 @@
         <v>28</v>
       </c>
       <c r="AT27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU27" t="n">
         <v>26</v>
       </c>
-      <c r="AU27" t="n">
-        <v>25</v>
-      </c>
       <c r="AV27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW27" t="n">
         <v>13</v>
@@ -5355,16 +5422,16 @@
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB27" t="n">
         <v>10</v>
       </c>
       <c r="BC27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>7.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5495,7 +5562,7 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM28" t="n">
         <v>6</v>
@@ -5507,7 +5574,7 @@
         <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
@@ -5519,7 +5586,7 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F29" t="n">
         <v>47</v>
       </c>
       <c r="G29" t="n">
-        <v>0.382</v>
+        <v>0.373</v>
       </c>
       <c r="H29" t="n">
         <v>48.8</v>
@@ -5602,19 +5669,19 @@
         <v>7</v>
       </c>
       <c r="M29" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0.339</v>
+        <v>0.34</v>
       </c>
       <c r="O29" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P29" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.785</v>
+        <v>0.786</v>
       </c>
       <c r="R29" t="n">
         <v>10.8</v>
@@ -5635,7 +5702,7 @@
         <v>7.3</v>
       </c>
       <c r="X29" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y29" t="n">
         <v>4.8</v>
@@ -5644,25 +5711,25 @@
         <v>22.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB29" t="n">
         <v>97</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
       </c>
       <c r="AF29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
@@ -5677,7 +5744,7 @@
         <v>22</v>
       </c>
       <c r="AL29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
@@ -5710,10 +5777,10 @@
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5722,7 +5789,7 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB29" t="n">
         <v>16</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E30" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F30" t="n">
         <v>37</v>
       </c>
       <c r="G30" t="n">
-        <v>0.519</v>
+        <v>0.513</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5775,28 +5842,28 @@
         <v>37.3</v>
       </c>
       <c r="J30" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L30" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M30" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="O30" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P30" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.762</v>
+        <v>0.764</v>
       </c>
       <c r="R30" t="n">
         <v>12.3</v>
@@ -5805,10 +5872,10 @@
         <v>29.8</v>
       </c>
       <c r="T30" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U30" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V30" t="n">
         <v>14.8</v>
@@ -5817,22 +5884,22 @@
         <v>8.4</v>
       </c>
       <c r="X30" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y30" t="n">
         <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA30" t="n">
         <v>20.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5841,13 +5908,13 @@
         <v>14</v>
       </c>
       <c r="AF30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI30" t="n">
         <v>14</v>
@@ -5859,19 +5926,19 @@
         <v>12</v>
       </c>
       <c r="AL30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM30" t="n">
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO30" t="n">
         <v>7</v>
       </c>
       <c r="AP30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ30" t="n">
         <v>13</v>
@@ -5904,13 +5971,13 @@
         <v>29</v>
       </c>
       <c r="BA30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB30" t="n">
         <v>13</v>
       </c>
       <c r="BC30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-2.3</v>
       </c>
       <c r="AD31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF31" t="n">
         <v>22</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>21</v>
       </c>
       <c r="AG31" t="n">
         <v>22</v>
@@ -6035,7 +6102,7 @@
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK31" t="n">
         <v>29</v>
@@ -6047,13 +6114,13 @@
         <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO31" t="n">
         <v>24</v>
       </c>
       <c r="AP31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ31" t="n">
         <v>22</v>
@@ -6077,7 +6144,7 @@
         <v>22</v>
       </c>
       <c r="AX31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY31" t="n">
         <v>9</v>
@@ -6089,7 +6156,7 @@
         <v>23</v>
       </c>
       <c r="BB31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-5-2012-13</t>
+          <t>2013-04-05</t>
         </is>
       </c>
     </row>
